--- a/光伏配储项目/电价数据/2026/新围站.xlsx
+++ b/光伏配储项目/电价数据/2026/新围站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5097200000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8061799999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6063099999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.61897</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51509</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50137</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45427</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39202</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41381</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44364</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11946</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09712999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10714</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09307</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.03902000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02849</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01998</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02054</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09025</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04128</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.06631999999999999</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.18187</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21909</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.0404</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.03643</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.03439</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27126</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.18968</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.02973</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.51025</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.71582</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.52699</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57229</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45739</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6122799999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80491</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6293099999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.62054</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7511599999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9487300000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.67092</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.57553</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.71302</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.55298</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.53447</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6379900000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6104400000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47129</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42563</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69433</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.37432</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.72475</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.12064</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.76735</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52089</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51885</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50822</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59148</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.01889</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.03349</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>-0.04862</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.01062</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.03099</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.15384</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.71839</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.73334</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.01191</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.49181</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.12604</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4872</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.22256</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.03831</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>-0.03775</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>-0.02379</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.55665</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.67831</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68899</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.73214</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73025</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.53987</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.50324</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7493200000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.07734000000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13752</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.13031</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.23233</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.06271</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33456</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="E119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47388</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20212</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47355</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48349</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.15809</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.26587</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47898</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52951</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61099</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5929</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.75554</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48807</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4387200000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42172</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.09903000000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.22047</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.22046</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.22294</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.03771</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.47866</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>-0.03703</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>-0.03772</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.02412</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07163</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.03938000000000001</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02339</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.00139</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.01483</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06276</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.02061</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.24934</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14818</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5599700000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4679</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.24648</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.23781</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.18422</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.19419</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.25083</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.18537</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29837</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04736</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04937</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.04316</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04964</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03262</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04022</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03786</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03849</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03922</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03671</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.03978</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04026</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04147</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.0402</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21899</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04953</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05603</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05684</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41742</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35111</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44715</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04347</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04608</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.02984</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04189</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10697</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-5e-05</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03669</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0424</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04367</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04557</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04313</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04034</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04522</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0396</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04159</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04977</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04767</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20008</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14297</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33577</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31789</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15882</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17115</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14789</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15962</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15879</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26912</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27113</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45405</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50768</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78103</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92041</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49457</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91596</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8680800000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29914</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89273</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63254</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19224</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87133</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5469700000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33611</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03654</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53604</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7954199999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53103</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7774500000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78108</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8773200000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8762000000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49732</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40527</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21238</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87902</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55113</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62719</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5396599999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49924</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45278</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40449</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58721</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59626</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6027400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67614</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46931</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41841</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58036</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45176</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88119</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6356000000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.6464800000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.62805</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86248</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44211</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35358</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92748</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46848</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16495</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1992</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20141</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29042</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40221</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5982499999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89071</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.42281</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.21563</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72809</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82843</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68237</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.60421</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.46278</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.46092</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.51586</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.44808</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.43299</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.51661</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44578</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4381</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.46237</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51463</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.03997</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>-0.009789999999999998</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.02427</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24285</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.00505</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.00605</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25929</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28645</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.23656</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.41186</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5770700000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.47258</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.83316</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32439</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27518</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.04904</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.11533</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.03264</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.06417</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.06382</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>-0.04986</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>-0.04899</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.04779</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04797</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.14444</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.15344</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.14703</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.16998</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.22042</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.20693</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40391</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45478</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34913</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5566599999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4815</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19699</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24775</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24035</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.66984</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.72848</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5275700000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36279</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25059</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>-0.04606</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22321</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45313</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7024400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50491</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28906</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34969</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65116</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81857</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44703</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46543</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3414</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40734</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19935</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22021</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27899</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43655</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48031</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.7537999999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5929099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.81728</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5979800000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7162200000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.66174</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.88501</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47876</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48028</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43088</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49062</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5190499999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.47818</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41087</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41537</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42642</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46104</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.57612</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.51552</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44471</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44315</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48057</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46295</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57464</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.45111</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6418400000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16844</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44307</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5038899999999999</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52928</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.69145</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7858099999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.6996</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.73999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80775</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.57799</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.51227</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7928500000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.73361</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62146</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65698</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47304</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46019</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.54883</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42936</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44221</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42142</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21248</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36416</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40598</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46592</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11354</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18147</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41659</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36605</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22855</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23034</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25018</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14049</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04344</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25141</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16933</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18286</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22909</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25065</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2641</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23256</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35073</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.18472</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.23102</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23757</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.01862</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12362</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.00277</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03947</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01622</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04144</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03894</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04788000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02475</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02834</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.10742</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00016</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02774</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04943</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0405</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18677</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.22213</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.25564</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28373</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2161</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.69559</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.52201</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.25405</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.74424</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.7604500000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.7396</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.6967100000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.22284</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23403</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.19398</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.19451</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.18072</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.00653</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.13141</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.03585</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.21549</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01653</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.19096</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.19668</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20427</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01215</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17386</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18002</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.21078</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32381</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.13327</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5296799999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5122000000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.42899</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44065</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14028</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27009</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32757</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.52662</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.51152</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.48751</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25963</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.48727</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.46146</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36724</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47879</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38178</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.45749</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49545</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5709299999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5663899999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.49376</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.56941</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49374</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.53047</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5589500000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5833700000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.65415</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.72127</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54838</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55103</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43873</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37218</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.13788</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.23833</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21207</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05856</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.14431</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02368</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20266</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00388</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25743</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15594</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05528</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04645000000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06439</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16178</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07217</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05436999999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18736</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14767</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37576</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.93331</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.50174</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45929</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.12312</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.02984</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.20121</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03111</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.009179999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01762</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01214</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00739</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.005900000000000001</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15561</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03828</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1704</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.47009</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40673</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49737</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37033</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.53914</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.16325</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.24396</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.26853</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13287</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.07452</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.10427</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04709000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04351</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.03867</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04031000000000001</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.08882</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10932</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.20409</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.23569</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.14082</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.27392</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14365</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04675</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.17721</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.13376</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.22189</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38873</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38687</v>
       </c>
     </row>
   </sheetData>
